--- a/Report/Components-List.xlsx
+++ b/Report/Components-List.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E850179A-7E04-4BFB-8869-37B5EDCB6FAC}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F51F1187-B8B7-4004-9AEB-E6668E964504}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Name</t>
   </si>
@@ -41,13 +41,22 @@
   </si>
   <si>
     <t>Total cost</t>
+  </si>
+  <si>
+    <t>2WD Robot Car Chassis Kit</t>
+  </si>
+  <si>
+    <t>Robot Smart Car 2WD With Advanced Metal Roller Caster Wheel</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/ro-base-2wd-2floor-2wd-robot-car-chassis-kit-with-speed-encoder-wheels-2-floor-7171</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -61,6 +70,20 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -92,10 +115,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -106,8 +130,24 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -389,202 +429,348 @@
   <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="10.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="33.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="42.88671875" style="1" customWidth="1"/>
+    <col min="3" max="5" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="18.21875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F2" s="1">
-        <f>D2*E2</f>
-        <v>0</v>
+    </row>
+    <row r="2" spans="1:10" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6">
+        <f>C2*D2</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F3" s="1">
-        <f t="shared" ref="F3:F28" si="0">D3*E3</f>
-        <v>0</v>
-      </c>
+      <c r="A3" s="6"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6">
+        <f t="shared" ref="E3:E28" si="0">C3*D3</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="6"/>
       <c r="J3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F4" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6"/>
       <c r="J4" s="3">
-        <f>SUM(F2:F35)</f>
+        <f>SUM(E2:E35)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F5" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6">
+        <f>C5*D5</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F6" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="6"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F7" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F8" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F9" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="6"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F10" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F11" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F12" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F13" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F14" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F15" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F16" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F17" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F18" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F19" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F20" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F21" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F22" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F23" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F24" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F25" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F26" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F27" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F28" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="6"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{016E39A5-076D-4789-9136-DD7E9D5C4229}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Report/Components-List.xlsx
+++ b/Report/Components-List.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F51F1187-B8B7-4004-9AEB-E6668E964504}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D177DDB-0F47-4302-A121-89F6DB17D8B3}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
   <si>
     <t>Name</t>
   </si>
@@ -50,6 +50,57 @@
   </si>
   <si>
     <t>https://www.ram-e-shop.com/shop/ro-base-2wd-2floor-2wd-robot-car-chassis-kit-with-speed-encoder-wheels-2-floor-7171</t>
+  </si>
+  <si>
+    <t>Sorce</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>RAM</t>
+  </si>
+  <si>
+    <t>Future</t>
+  </si>
+  <si>
+    <t>The chassis plates are cut from acrylic with a wide variety of mounting holes for sensors, controllers, power, etc. Simply bolt the two pre-cut platforms together</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/robot-platform-2-gear-motors-2-wheels-castor?_pos=2&amp;_sid=596ca3e3a&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>IR Infrared 3-pin</t>
+  </si>
+  <si>
+    <t>Object Detection Sensor</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/kit-object-ir-ir-infrared-3-pin-obstacle-avoidance-sku-object-7079</t>
+  </si>
+  <si>
+    <t>IR Infrared 4-pin</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/kit-ky032-4pin-object-ir-infrared-4-pin-obstacle-avoidance-sku-ky032-7751</t>
+  </si>
+  <si>
+    <t>IR LED Receiver</t>
+  </si>
+  <si>
+    <t>5mm Infrared Receiver</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/ir-led-black-5mm-ir-led-5mm-infrared-receiver-5960</t>
+  </si>
+  <si>
+    <t>IR LED Transmitter</t>
+  </si>
+  <si>
+    <t>5mm Infrared Transmitter</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/ir-led-white-5mm-ir-led-5mm-infrared-transmitter-5662</t>
   </si>
 </sst>
 </file>
@@ -119,7 +170,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -141,9 +192,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -426,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.6640625" style="1" customWidth="1"/>
@@ -436,7 +484,7 @@
     <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -455,131 +503,235 @@
       <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G1" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+      <c r="C2" s="6">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6">
+        <v>350</v>
+      </c>
       <c r="E2" s="6">
         <f>C2*D2</f>
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="6">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <v>260</v>
+      </c>
       <c r="E3" s="6">
         <f t="shared" ref="E3:E28" si="0">C3*D3</f>
-        <v>0</v>
-      </c>
-      <c r="F3" s="6"/>
+        <v>260</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="J3" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
+      <c r="K3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="6">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6">
+        <v>35</v>
+      </c>
       <c r="E4" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F4" s="6"/>
+        <v>35</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="J4" s="3">
         <f>SUM(E2:E35)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
+        <v>695</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6">
+        <v>45</v>
+      </c>
       <c r="E5" s="6">
         <f>C5*D5</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
+        <v>45</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6">
+        <v>3</v>
+      </c>
       <c r="E6" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F6" s="6"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6">
+        <v>2</v>
+      </c>
       <c r="E7" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
+      <c r="C8" s="6">
+        <v>1</v>
+      </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F8" s="7"/>
+      <c r="G8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
+      <c r="C9" s="6">
+        <v>1</v>
+      </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F9" s="7"/>
+      <c r="G9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
+      <c r="C10" s="6">
+        <v>1</v>
+      </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F10" s="7"/>
+      <c r="G10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
+      <c r="C11" s="6">
+        <v>1</v>
+      </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F11" s="7"/>
+      <c r="G11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -588,9 +740,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F12" s="7"/>
+      <c r="G12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -599,9 +754,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F13" s="7"/>
+      <c r="G13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -611,8 +769,11 @@
         <v>0</v>
       </c>
       <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G14" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -622,8 +783,11 @@
         <v>0</v>
       </c>
       <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G15" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -633,8 +797,11 @@
         <v>0</v>
       </c>
       <c r="F16" s="6"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -644,8 +811,11 @@
         <v>0</v>
       </c>
       <c r="F17" s="6"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -655,8 +825,11 @@
         <v>0</v>
       </c>
       <c r="F18" s="6"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -666,8 +839,11 @@
         <v>0</v>
       </c>
       <c r="F19" s="6"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -677,8 +853,11 @@
         <v>0</v>
       </c>
       <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -688,8 +867,11 @@
         <v>0</v>
       </c>
       <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -699,8 +881,11 @@
         <v>0</v>
       </c>
       <c r="F22" s="6"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -711,7 +896,7 @@
       </c>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -722,7 +907,7 @@
       </c>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -733,7 +918,7 @@
       </c>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -744,7 +929,7 @@
       </c>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -755,7 +940,7 @@
       </c>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -767,10 +952,15 @@
       <c r="F28" s="6"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G22" xr:uid="{9524383D-FF88-4EBF-A2C1-6C00F40D5ACB}">
+      <formula1>$K$4:$K$5</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{016E39A5-076D-4789-9136-DD7E9D5C4229}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Report/Components-List.xlsx
+++ b/Report/Components-List.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D177DDB-0F47-4302-A121-89F6DB17D8B3}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73238CFD-FAEE-4F0B-A87A-BE651DEC823A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
   <si>
     <t>Name</t>
   </si>
@@ -101,6 +101,42 @@
   </si>
   <si>
     <t>https://www.ram-e-shop.com/shop/ir-led-white-5mm-ir-led-5mm-infrared-transmitter-5662</t>
+  </si>
+  <si>
+    <t>Reflective IR sensor</t>
+  </si>
+  <si>
+    <t>The TCRT5000 Reflective IR sensor photoelectric switch is perfect for line tracking robot car like DIY projects. It include an infrared emitter and phototransistor in a leaded package which blocks visible light.</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/tcrt5000-reflective-ir-sensor?_pos=1&amp;_sid=b6ce8bdf0&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>Line Tracker (Finder) Sensor</t>
+  </si>
+  <si>
+    <t>This is high performance line finder that is designed for line following robotic. It consists two parts - an IR emitting LED and an IR sensitive phototransistor</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/line-tracker-finder-sensor?_pos=4&amp;_sid=32a758820&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>Infrared Obstacle Avoidance Sensor (KY-032)</t>
+  </si>
+  <si>
+    <t>Ky-032 is an infrared obstacle avoisance sensor. I can sense obstacles in front of moving robot at distance up to 40cm. The object (obstacle) detection distance can be adjusted using potentiometer. Infrared is emitted at a certain frequency, </t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/infrared-obstacle-avoidance-sensor-ky-032?_pos=7&amp;_sid=32a758820&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>Line Tracker (Follower) Module - KY033</t>
+  </si>
+  <si>
+    <t>KY033 is a fairly accurate  line tracker that is designed for line following 4 wheels and two wheels moving robotics . It consists two parts: an IR emitting LED and an IR sensitive phototransistor.</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/line-tracker-follower-module-ky033?_pos=8&amp;_sid=32a758820&amp;_ss=r</t>
   </si>
 </sst>
 </file>
@@ -477,11 +513,17 @@
   <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.88671875" style="1" customWidth="1"/>
-    <col min="3" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="6" width="18.21875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="33.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.88671875" style="1"/>
+    <col min="10" max="10" width="9.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -586,7 +628,7 @@
       </c>
       <c r="J4" s="3">
         <f>SUM(E2:E35)</f>
-        <v>695</v>
+        <v>890</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>12</v>
@@ -667,74 +709,108 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+    <row r="8" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>28</v>
+      </c>
       <c r="C8" s="6">
         <v>1</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="6">
+        <v>20</v>
+      </c>
       <c r="E8" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F8" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="G8" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="C9" s="6">
         <v>1</v>
       </c>
-      <c r="D9" s="6"/>
+      <c r="D9" s="6">
+        <v>60</v>
+      </c>
       <c r="E9" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="7"/>
+        <v>60</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="G9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="C10" s="6">
         <v>1</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="6">
+        <v>75</v>
+      </c>
       <c r="E10" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="7"/>
+        <v>75</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>35</v>
+      </c>
       <c r="G10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>37</v>
+      </c>
       <c r="C11" s="6">
         <v>1</v>
       </c>
-      <c r="D11" s="6"/>
+      <c r="D11" s="6">
+        <v>40</v>
+      </c>
       <c r="E11" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="G11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
+      <c r="C12" s="6">
+        <v>1</v>
+      </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6">
         <f t="shared" si="0"/>
@@ -742,13 +818,15 @@
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6">
         <f t="shared" si="0"/>
@@ -756,13 +834,15 @@
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
+      <c r="C14" s="6">
+        <v>1</v>
+      </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6">
         <f t="shared" si="0"/>
@@ -770,13 +850,15 @@
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
+      <c r="C15" s="6">
+        <v>1</v>
+      </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6">
         <f t="shared" si="0"/>
@@ -784,13 +866,15 @@
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
+      <c r="C16" s="6">
+        <v>1</v>
+      </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6">
         <f t="shared" si="0"/>
@@ -798,7 +882,7 @@
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -812,7 +896,7 @@
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -826,7 +910,7 @@
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">

--- a/Report/Components-List.xlsx
+++ b/Report/Components-List.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73238CFD-FAEE-4F0B-A87A-BE651DEC823A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF62590-B440-4272-9C21-1BD31354E736}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="66">
   <si>
     <t>Name</t>
   </si>
@@ -137,13 +137,94 @@
   </si>
   <si>
     <t>https://store.fut-electronics.com/products/line-tracker-follower-module-ky033?_pos=8&amp;_sid=32a758820&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>L298 Dual H-Bridge Motor Driver</t>
+  </si>
+  <si>
+    <t>The Dual H-Bridge Motor Driver module Board, using ST's L298N chip can directly drive two 3-30V DC motor. You can easily control the DC motor speed and direction, you can also control the 2-phase stepper motor, smart car essential. </t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/l298-dual-h-bridge-motor-driver-dc-and-stepper-motors?_pos=1&amp;_sid=d332ff26a&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/dc-geared-motors-for-robots-straight-shaft?_pos=2&amp;_sid=d332ff26a&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>DC Geared Motors for Robots</t>
+  </si>
+  <si>
+    <t>This DC geared motor can be connectid directly to our robot tires without any couplings.</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/micro-servo-motor-1-3kg-cm?_pos=3&amp;_sid=d332ff26a&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>Micro Servo Motor </t>
+  </si>
+  <si>
+    <t>Unlike dc motors, with servo motors you can position the motor shaft at a specific position (angle) using control signal</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/l293d-dual-motor-driver-with-thermal-shutdown?_pos=4&amp;_sid=d332ff26a&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>L293D DUAL Motor Driver</t>
+  </si>
+  <si>
+    <t>L293D ia a PUSH-PULL FOUR CHANNEL DRIVER WITH DIODES  </t>
+  </si>
+  <si>
+    <t>Micro Metal Gear DC Motor</t>
+  </si>
+  <si>
+    <t>N20-6V-30 Rpm Micro Metal Gear Motor is a small volume, big torsion, all metal gear</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/micro-metal-gear-dc-motor-120-rpm?_pos=5&amp;_sid=d332ff26a&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/stepper-motor-driver-board-uln2003?_pos=6&amp;_sid=d332ff26a&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>Stepper Motor Driver Board ULN2003</t>
+  </si>
+  <si>
+    <t>ULN2003 Stepper Motor Driver Board is use the ULN2003 DARLINGTON ARRAYS to drive the 4-phase 5-wire stepper motor (5v-12v), up to 0.5A.</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/simple-dc-motor?_pos=8&amp;_sid=d332ff26a&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>Simple DC Motor</t>
+  </si>
+  <si>
+    <t>Max Speed: 12800 RPM</t>
+  </si>
+  <si>
+    <t>Mini Vibration Motor</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/mini-vibration-motor?_pos=9&amp;_sid=d332ff26a&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>This low cost vibration motor  can be used in many applications. </t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/l298-dual-motor-driver-module-2a?_pos=10&amp;_sid=d332ff26a&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>L298 Dual Motor Driver Module 2A</t>
+  </si>
+  <si>
+    <t>This driver module is based on L298N H-bridge, a high current, high voltage dual full bridge driver manufactured by ST company.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,6 +252,12 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="17"/>
+      <color rgb="FF333333"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -206,7 +293,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -227,6 +314,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -510,6 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -550,7 +644,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -573,8 +667,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -603,8 +697,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -628,14 +722,14 @@
       </c>
       <c r="J4" s="3">
         <f>SUM(E2:E35)</f>
-        <v>890</v>
+        <v>1520</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -661,8 +755,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -685,8 +779,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -709,8 +803,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -733,8 +827,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
         <v>30</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -758,7 +852,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -782,7 +876,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="9" t="s">
         <v>36</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -805,172 +899,256 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
+    <row r="12" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="C12" s="6">
         <v>1</v>
       </c>
-      <c r="D12" s="6"/>
+      <c r="D12" s="6">
+        <v>130</v>
+      </c>
       <c r="E12" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F12" s="7"/>
+        <v>130</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="G12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+    <row r="13" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="C13" s="6">
         <v>1</v>
       </c>
-      <c r="D13" s="6"/>
+      <c r="D13" s="6">
+        <v>35</v>
+      </c>
       <c r="E13" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="7"/>
+        <v>35</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="G13" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
+    <row r="14" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="C14" s="6">
         <v>1</v>
       </c>
-      <c r="D14" s="6"/>
+      <c r="D14" s="6">
+        <v>85</v>
+      </c>
       <c r="E14" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="6"/>
+        <v>85</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="G14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
+    <row r="15" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="C15" s="6">
         <v>1</v>
       </c>
-      <c r="D15" s="6"/>
+      <c r="D15" s="6">
+        <v>30</v>
+      </c>
       <c r="E15" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F15" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="G15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
+    <row r="16" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="C16" s="6">
         <v>1</v>
       </c>
-      <c r="D16" s="6"/>
+      <c r="D16" s="6">
+        <v>160</v>
+      </c>
       <c r="E16" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="6"/>
+        <v>160</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="G16" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
+    <row r="17" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1</v>
+      </c>
+      <c r="D17" s="6">
+        <v>30</v>
+      </c>
       <c r="E17" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="6"/>
+        <v>30</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="G17" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
+    <row r="18" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1</v>
+      </c>
+      <c r="D18" s="6">
+        <v>40</v>
+      </c>
       <c r="E18" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F18" s="6"/>
+        <v>40</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="G18" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
+    <row r="19" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1</v>
+      </c>
+      <c r="D19" s="6">
+        <v>40</v>
+      </c>
       <c r="E19" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="6"/>
+        <v>40</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="G19" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1</v>
+      </c>
+      <c r="D20" s="6">
+        <v>80</v>
+      </c>
       <c r="E20" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="G20" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
       <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
+      <c r="C21" s="6">
+        <v>1</v>
+      </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F21" s="6"/>
+      <c r="F21" s="7"/>
       <c r="G21" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
       <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
+      <c r="C22" s="6">
+        <v>1</v>
+      </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F22" s="6"/>
+      <c r="F22" s="7"/>
       <c r="G22" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="9"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -978,7 +1156,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F23" s="6"/>
+      <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
@@ -1043,8 +1221,9 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{016E39A5-076D-4789-9136-DD7E9D5C4229}"/>
+    <hyperlink ref="F17" r:id="rId2" xr:uid="{452069C4-3A92-4021-AFA9-BC017FC08004}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/Report/Components-List.xlsx
+++ b/Report/Components-List.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF62590-B440-4272-9C21-1BD31354E736}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA48431-9900-45EC-B722-BF357CEDEC02}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="97">
   <si>
     <t>Name</t>
   </si>
@@ -218,6 +218,99 @@
   </si>
   <si>
     <t>This driver module is based on L298N H-bridge, a high current, high voltage dual full bridge driver manufactured by ST company.</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>chassis</t>
+  </si>
+  <si>
+    <t>IR sensor</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>Wheel</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>Motor Driver</t>
+  </si>
+  <si>
+    <t>25GA370 DC Geared</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/dc-jga25-370-enc-12v130r-25ga370-dc-geared-motor-with-encoder-12vdc-130-rpm-9331</t>
+  </si>
+  <si>
+    <t>25GA370 DC Geared Motor With Encoder 12Vdc 130 rpm</t>
+  </si>
+  <si>
+    <t>DC Geared Motor JGB37555</t>
+  </si>
+  <si>
+    <t>DC Geared Motor 12Vdc 267 rpm - Model JGB37555-18.75K</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/dc-jgb37555-12v267r-dc-geared-motor-12vdc-267-rpm-model-jgb37555-18-75k-9333</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/dc-sg555123000-10k-dc-geared-motor-12vdc-300-rpm-0-13-n-m-model-sg555123000-10k-6688</t>
+  </si>
+  <si>
+    <t>DC Geared Motor SG555123000</t>
+  </si>
+  <si>
+    <t>DC Geared Motor 12Vdc 300 rpm 0.13 N.m - Model SG555123000-10K</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/dc-motor-27127600-186k-dc-geared-motor-12vdc-50-rpm-0-127-n-m-model-dcm27127600-186k-6245</t>
+  </si>
+  <si>
+    <t>DC Geared Motor DCM27127600</t>
+  </si>
+  <si>
+    <t>DC Geared Motor 12Vdc 50 rpm 0.127 N.m - Model DCM27127600-186K</t>
+  </si>
+  <si>
+    <t>DC Motor 775</t>
+  </si>
+  <si>
+    <t>DC Motor 12V 80W 13000 rpm - Model 775 Motor (High Speed Motor)</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/dc-775-80w-13000rpm-dc-motor-12v-80w-13000-rpm-model-775-motor-high-speed-motor-7871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC Motor RS390 </t>
+  </si>
+  <si>
+    <t>DC Motor 6V 18000 rpm - Model RS390 Motor (High Speed Motor)</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/dc-rs390-6vdc-dc-motor-6v-18000-rpm-model-rs390-motor-high-speed-motor-8568</t>
+  </si>
+  <si>
+    <t>JGB37-520 Self-Balancing Geared Motor</t>
+  </si>
+  <si>
+    <t>JGB37-520 Self-Balancing Geared Motor 12Vdc 107 rpm Torque 4.8 kg.cm - With Hall Encoder</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/dc-jgb37520-self-balance-12v-jgb37-520-self-balancing-geared-motor-12vdc-107-rpm-torque-4-8-kg-cm-with-hall-encoder-9322</t>
+  </si>
+  <si>
+    <t>DC Geared Motor GA12-N20</t>
+  </si>
+  <si>
+    <t>Micro Metal 12V DC Geared Motor 35 rpm (GA12-N20)</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/dc-micro-n20-12v-35rpm-micro-metal-12v-dc-geared-motor-35-rpm-ga12-n20-9339</t>
   </si>
 </sst>
 </file>
@@ -604,7 +697,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -614,13 +707,15 @@
     <col min="5" max="5" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.88671875" style="1"/>
+    <col min="8" max="8" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="1"/>
     <col min="10" max="10" width="9.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="1"/>
+    <col min="12" max="12" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -642,8 +737,11 @@
       <c r="G1" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H1" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
@@ -666,8 +764,11 @@
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="H2" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>7</v>
       </c>
@@ -681,7 +782,7 @@
         <v>260</v>
       </c>
       <c r="E3" s="6">
-        <f t="shared" ref="E3:E28" si="0">C3*D3</f>
+        <f t="shared" ref="E3:E40" si="0">C3*D3</f>
         <v>260</v>
       </c>
       <c r="F3" s="7" t="s">
@@ -690,14 +791,20 @@
       <c r="G3" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="L3" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>16</v>
       </c>
@@ -720,15 +827,21 @@
       <c r="G4" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="J4" s="3">
         <f>SUM(E2:E35)</f>
-        <v>1520</v>
+        <v>5645</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="L4" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>19</v>
       </c>
@@ -751,11 +864,17 @@
       <c r="G5" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H5" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="K5" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="L5" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>21</v>
       </c>
@@ -778,8 +897,14 @@
       <c r="G6" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>24</v>
       </c>
@@ -802,8 +927,14 @@
       <c r="G7" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="H7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>27</v>
       </c>
@@ -826,8 +957,14 @@
       <c r="G8" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="H8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>30</v>
       </c>
@@ -850,8 +987,14 @@
       <c r="G9" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="H9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>33</v>
       </c>
@@ -874,8 +1017,11 @@
       <c r="G10" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="H10" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>36</v>
       </c>
@@ -898,8 +1044,11 @@
       <c r="G11" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="H11" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>39</v>
       </c>
@@ -922,8 +1071,11 @@
       <c r="G12" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="H12" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>43</v>
       </c>
@@ -946,8 +1098,11 @@
       <c r="G13" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="H13" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>46</v>
       </c>
@@ -970,8 +1125,11 @@
       <c r="G14" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="H14" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>49</v>
       </c>
@@ -994,8 +1152,11 @@
       <c r="G15" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="H15" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>51</v>
       </c>
@@ -1018,8 +1179,11 @@
       <c r="G16" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="H16" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>55</v>
       </c>
@@ -1042,8 +1206,11 @@
       <c r="G17" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="H17" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>58</v>
       </c>
@@ -1066,8 +1233,11 @@
       <c r="G18" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="H18" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>60</v>
       </c>
@@ -1090,8 +1260,11 @@
       <c r="G19" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="H19" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>64</v>
       </c>
@@ -1114,109 +1287,376 @@
       <c r="G20" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="6"/>
+      <c r="H20" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A21" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="C21" s="6">
         <v>1</v>
       </c>
-      <c r="D21" s="6"/>
+      <c r="D21" s="6">
+        <v>500</v>
+      </c>
       <c r="E21" s="6">
         <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1</v>
+      </c>
+      <c r="D22" s="6">
+        <v>600</v>
+      </c>
+      <c r="E22" s="6">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1</v>
+      </c>
+      <c r="D23" s="6">
+        <v>850</v>
+      </c>
+      <c r="E23" s="6">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1</v>
+      </c>
+      <c r="D24" s="6">
+        <v>350</v>
+      </c>
+      <c r="E24" s="6">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1</v>
+      </c>
+      <c r="D25" s="6">
+        <v>450</v>
+      </c>
+      <c r="E25" s="6">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="6">
+        <v>1</v>
+      </c>
+      <c r="D26" s="6">
+        <v>350</v>
+      </c>
+      <c r="E26" s="6">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="6">
+        <v>1</v>
+      </c>
+      <c r="D27" s="6">
+        <v>750</v>
+      </c>
+      <c r="E27" s="6">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A28" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="6">
+        <v>1</v>
+      </c>
+      <c r="D28" s="6">
+        <v>275</v>
+      </c>
+      <c r="E28" s="6">
+        <f t="shared" si="0"/>
+        <v>275</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="C29" s="6">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6">
-        <v>1</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6">
+      <c r="G29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="C30" s="6">
+        <v>1</v>
+      </c>
+      <c r="E30" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6">
+      <c r="G30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="C31" s="6">
+        <v>1</v>
+      </c>
+      <c r="E31" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6">
+      <c r="G31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="9"/>
+      <c r="C32" s="6">
+        <v>1</v>
+      </c>
+      <c r="E32" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F24" s="6"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6">
+      <c r="G32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="C33" s="6">
+        <v>1</v>
+      </c>
+      <c r="E33" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F25" s="6"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6">
+      <c r="G33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="9"/>
+      <c r="C34" s="6">
+        <v>1</v>
+      </c>
+      <c r="E34" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F26" s="6"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6">
+      <c r="H34" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="E35" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F27" s="6"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6">
+      <c r="H35" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="9"/>
+      <c r="E36" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F28" s="6"/>
+      <c r="H36" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="9"/>
+      <c r="E37" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="9"/>
+      <c r="E38" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="E39" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E40" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G22" xr:uid="{9524383D-FF88-4EBF-A2C1-6C00F40D5ACB}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{9524383D-FF88-4EBF-A2C1-6C00F40D5ACB}">
       <formula1>$K$4:$K$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37:H57" xr:uid="{D626CD92-1D31-4F2E-84BE-B83415C68F3E}">
+      <formula1>$L$4:$L$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H36" xr:uid="{688D04B9-EF58-4BA7-8B5E-526FB7D00083}">
+      <formula1>$L$4:$L$9</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>

--- a/Report/Components-List.xlsx
+++ b/Report/Components-List.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA48431-9900-45EC-B722-BF357CEDEC02}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C8ED46-CFA6-4E84-834A-10F8D88C6726}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="114">
   <si>
     <t>Name</t>
   </si>
@@ -139,15 +139,6 @@
     <t>https://store.fut-electronics.com/products/line-tracker-follower-module-ky033?_pos=8&amp;_sid=32a758820&amp;_ss=r</t>
   </si>
   <si>
-    <t>L298 Dual H-Bridge Motor Driver</t>
-  </si>
-  <si>
-    <t>The Dual H-Bridge Motor Driver module Board, using ST's L298N chip can directly drive two 3-30V DC motor. You can easily control the DC motor speed and direction, you can also control the 2-phase stepper motor, smart car essential. </t>
-  </si>
-  <si>
-    <t>https://store.fut-electronics.com/products/l298-dual-h-bridge-motor-driver-dc-and-stepper-motors?_pos=1&amp;_sid=d332ff26a&amp;_ss=r</t>
-  </si>
-  <si>
     <t>https://store.fut-electronics.com/products/dc-geared-motors-for-robots-straight-shaft?_pos=2&amp;_sid=d332ff26a&amp;_ss=r</t>
   </si>
   <si>
@@ -311,6 +302,66 @@
   </si>
   <si>
     <t>https://www.ram-e-shop.com/shop/dc-micro-n20-12v-35rpm-micro-metal-12v-dc-geared-motor-35-rpm-ga12-n20-9339</t>
+  </si>
+  <si>
+    <t>Small Stepper Motor Driver</t>
+  </si>
+  <si>
+    <t>5V Small Stepper Motor Driver (SKU#M36)</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/kit-m36-step-uln2003-5v-small-stepper-motor-driver-sku-m36-7082</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/kit-a4988-driver-a4988-stepper-motor-driver-7155</t>
+  </si>
+  <si>
+    <t>A4988 Stepper Motor Driver</t>
+  </si>
+  <si>
+    <t>Reprap Driver A4988 Stepper Motor Driver Module</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/kit-l293d-blue-l293d-expansion-board-module-sku-k293-8238</t>
+  </si>
+  <si>
+    <t>L293D Expansion Board Module</t>
+  </si>
+  <si>
+    <t>L293D Expansion Board Module (SKU#K293) 4 Channel Motor Driver H-Bridge</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/kit-l298-big-red-l298-big-module-red-board-dual-h-bridge-motor-driver-using-l298n-7634</t>
+  </si>
+  <si>
+    <t>L298 Big Module Red Board</t>
+  </si>
+  <si>
+    <t>L298 Big Module Red Board (Dual H-Bridge Motor Driver Using L298N)</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/l293d-dual-motor-driver-with-thermal-shutdown?_pos=2&amp;_sid=6e81b72a6&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>L293D DUAL Motor Driver With Thermal Shutdown</t>
+  </si>
+  <si>
+    <t>L293B - 1A ( PUSH-PULL FOUR CHANNEL DRIVERS)</t>
+  </si>
+  <si>
+    <t>The L293B can be used as DC motors driver (control speed and direction). It is also used as a bipolar stepper motor driver, relays driver, solenoids driver and big LED driver.</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/l293b-1a-dual-motor-driver?_pos=15&amp;_sid=6e81b72a6&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>L297 Stepper Motor Controller IC</t>
+  </si>
+  <si>
+    <t>The L297 integrates all the control circuitry required to control bipolar and unipolar stepper motors</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/l297-stepper-motor-controller-ic?_pos=16&amp;_sid=6e81b72a6&amp;_ss=r</t>
   </si>
 </sst>
 </file>
@@ -697,7 +748,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -738,7 +789,7 @@
         <v>10</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -765,7 +816,7 @@
         <v>12</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
@@ -782,7 +833,7 @@
         <v>260</v>
       </c>
       <c r="E3" s="6">
-        <f t="shared" ref="E3:E40" si="0">C3*D3</f>
+        <f t="shared" ref="E3:E44" si="0">C3*D3</f>
         <v>260</v>
       </c>
       <c r="F3" s="7" t="s">
@@ -792,7 +843,7 @@
         <v>13</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>6</v>
@@ -801,7 +852,7 @@
         <v>11</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
@@ -828,17 +879,17 @@
         <v>12</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J4" s="3">
-        <f>SUM(E2:E35)</f>
-        <v>5645</v>
+        <f>SUM(E2:E34)</f>
+        <v>5960</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="72" x14ac:dyDescent="0.3">
@@ -865,13 +916,13 @@
         <v>12</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
@@ -898,10 +949,10 @@
         <v>12</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
@@ -928,10 +979,10 @@
         <v>12</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="72" x14ac:dyDescent="0.3">
@@ -958,10 +1009,10 @@
         <v>13</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="72" x14ac:dyDescent="0.3">
@@ -988,10 +1039,10 @@
         <v>13</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
@@ -1018,7 +1069,7 @@
         <v>13</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="72" x14ac:dyDescent="0.3">
@@ -1045,37 +1096,37 @@
         <v>13</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6">
+        <v>35</v>
+      </c>
+      <c r="E12" s="6">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6">
-        <v>130</v>
-      </c>
-      <c r="E12" s="6">
-        <f t="shared" si="0"/>
-        <v>130</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>41</v>
-      </c>
       <c r="G12" s="1" t="s">
         <v>13</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>43</v>
       </c>
@@ -1086,11 +1137,11 @@
         <v>1</v>
       </c>
       <c r="D13" s="6">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="E13" s="6">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>42</v>
@@ -1099,10 +1150,10 @@
         <v>13</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>46</v>
       </c>
@@ -1113,11 +1164,11 @@
         <v>1</v>
       </c>
       <c r="D14" s="6">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="E14" s="6">
         <f t="shared" si="0"/>
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>45</v>
@@ -1126,61 +1177,61 @@
         <v>13</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="6">
+        <v>1</v>
+      </c>
+      <c r="D15" s="6">
+        <v>160</v>
+      </c>
+      <c r="E15" s="6">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="6">
-        <v>1</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="G15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6">
         <v>30</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E16" s="6">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
+      <c r="F16" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="6">
-        <v>1</v>
-      </c>
-      <c r="D16" s="6">
-        <v>160</v>
-      </c>
-      <c r="E16" s="6">
-        <f t="shared" si="0"/>
-        <v>160</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>53</v>
-      </c>
       <c r="G16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -1194,11 +1245,11 @@
         <v>1</v>
       </c>
       <c r="D17" s="6">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E17" s="6">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>54</v>
@@ -1207,12 +1258,12 @@
         <v>13</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>59</v>
@@ -1228,18 +1279,18 @@
         <v>40</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
-        <v>60</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>62</v>
@@ -1248,14 +1299,14 @@
         <v>1</v>
       </c>
       <c r="D19" s="6">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E19" s="6">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>13</v>
@@ -1264,31 +1315,31 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
-        <v>64</v>
+    <row r="20" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C20" s="6">
         <v>1</v>
       </c>
       <c r="D20" s="6">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="E20" s="6">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -1296,53 +1347,53 @@
         <v>73</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1</v>
+      </c>
+      <c r="D21" s="6">
+        <v>600</v>
+      </c>
+      <c r="E21" s="6">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>75</v>
-      </c>
-      <c r="C21" s="6">
-        <v>1</v>
-      </c>
-      <c r="D21" s="6">
-        <v>500</v>
-      </c>
-      <c r="E21" s="6">
-        <f t="shared" si="0"/>
-        <v>500</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>74</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1</v>
+      </c>
+      <c r="D22" s="6">
+        <v>850</v>
+      </c>
+      <c r="E22" s="6">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" s="6">
-        <v>1</v>
-      </c>
-      <c r="D22" s="6">
-        <v>600</v>
-      </c>
-      <c r="E22" s="6">
-        <f t="shared" si="0"/>
-        <v>600</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>78</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -1356,11 +1407,11 @@
         <v>1</v>
       </c>
       <c r="D23" s="6">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="E23" s="6">
         <f t="shared" si="0"/>
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>79</v>
@@ -1369,37 +1420,37 @@
         <v>12</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="C24" s="6">
+        <v>1</v>
+      </c>
+      <c r="D24" s="6">
+        <v>450</v>
+      </c>
+      <c r="E24" s="6">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="C24" s="6">
-        <v>1</v>
-      </c>
-      <c r="D24" s="6">
-        <v>350</v>
-      </c>
-      <c r="E24" s="6">
-        <f t="shared" si="0"/>
-        <v>350</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>85</v>
       </c>
@@ -1410,11 +1461,11 @@
         <v>1</v>
       </c>
       <c r="D25" s="6">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="E25" s="6">
         <f t="shared" si="0"/>
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>87</v>
@@ -1423,10 +1474,10 @@
         <v>12</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>88</v>
       </c>
@@ -1437,11 +1488,11 @@
         <v>1</v>
       </c>
       <c r="D26" s="6">
-        <v>350</v>
+        <v>750</v>
       </c>
       <c r="E26" s="6">
         <f t="shared" si="0"/>
-        <v>350</v>
+        <v>750</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>90</v>
@@ -1450,10 +1501,10 @@
         <v>12</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>91</v>
       </c>
@@ -1464,11 +1515,11 @@
         <v>1</v>
       </c>
       <c r="D27" s="6">
-        <v>750</v>
+        <v>275</v>
       </c>
       <c r="E27" s="6">
         <f t="shared" si="0"/>
-        <v>750</v>
+        <v>275</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>93</v>
@@ -1477,25 +1528,25 @@
         <v>12</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C28" s="6">
         <v>1</v>
       </c>
-      <c r="D28" s="6">
-        <v>275</v>
+      <c r="D28" s="1">
+        <v>30</v>
       </c>
       <c r="E28" s="6">
         <f t="shared" si="0"/>
-        <v>275</v>
+        <v>30</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>96</v>
@@ -1507,14 +1558,25 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
+    <row r="29" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="C29" s="6">
         <v>1</v>
       </c>
+      <c r="D29" s="1">
+        <v>85</v>
+      </c>
       <c r="E29" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>12</v>
@@ -1523,14 +1585,25 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
+    <row r="30" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="C30" s="6">
         <v>1</v>
       </c>
+      <c r="D30" s="1">
+        <v>75</v>
+      </c>
       <c r="E30" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>12</v>
@@ -1539,14 +1612,25 @@
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
+    <row r="31" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>105</v>
+      </c>
       <c r="C31" s="6">
         <v>1</v>
       </c>
+      <c r="D31" s="1">
+        <v>140</v>
+      </c>
       <c r="E31" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>140</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>12</v>
@@ -1555,46 +1639,82 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
+    <row r="32" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="C32" s="6">
         <v>1</v>
       </c>
+      <c r="D32" s="1">
+        <v>30</v>
+      </c>
       <c r="E32" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>106</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
+    <row r="33" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="C33" s="6">
         <v>1</v>
       </c>
+      <c r="D33" s="1">
+        <v>65</v>
+      </c>
       <c r="E33" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>65</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="9"/>
+    <row r="34" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A34" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="C34" s="6">
         <v>1</v>
       </c>
+      <c r="D34" s="1">
+        <v>20</v>
+      </c>
       <c r="E34" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>69</v>
@@ -1602,9 +1722,15 @@
     </row>
     <row r="35" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A35" s="9"/>
+      <c r="C35" s="6">
+        <v>1</v>
+      </c>
       <c r="E35" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>69</v>
@@ -1612,56 +1738,100 @@
     </row>
     <row r="36" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
+      <c r="C36" s="6">
+        <v>1</v>
+      </c>
       <c r="E36" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>69</v>
+      <c r="G36" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
+      <c r="C37" s="6">
+        <v>1</v>
+      </c>
       <c r="E37" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
+      <c r="C38" s="6">
+        <v>1</v>
+      </c>
       <c r="E38" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="9"/>
+      <c r="G38" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C39" s="6">
+        <v>1</v>
+      </c>
       <c r="E39" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E40" s="6">
+        <f>C40*D40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E41" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E42" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E43" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E44" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{9524383D-FF88-4EBF-A2C1-6C00F40D5ACB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36:H56" xr:uid="{D626CD92-1D31-4F2E-84BE-B83415C68F3E}">
+      <formula1>$L$4:$L$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G39" xr:uid="{9524383D-FF88-4EBF-A2C1-6C00F40D5ACB}">
       <formula1>$K$4:$K$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H37:H57" xr:uid="{D626CD92-1D31-4F2E-84BE-B83415C68F3E}">
-      <formula1>$L$4:$L$7</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H36" xr:uid="{688D04B9-EF58-4BA7-8B5E-526FB7D00083}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H35" xr:uid="{688D04B9-EF58-4BA7-8B5E-526FB7D00083}">
       <formula1>$L$4:$L$9</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{016E39A5-076D-4789-9136-DD7E9D5C4229}"/>
-    <hyperlink ref="F17" r:id="rId2" xr:uid="{452069C4-3A92-4021-AFA9-BC017FC08004}"/>
+    <hyperlink ref="F16" r:id="rId2" xr:uid="{452069C4-3A92-4021-AFA9-BC017FC08004}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>

--- a/Report/Components-List.xlsx
+++ b/Report/Components-List.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C8ED46-CFA6-4E84-834A-10F8D88C6726}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073D27B3-1EED-4585-823D-C7BB3E295CA5}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="145">
   <si>
     <t>Name</t>
   </si>
@@ -362,6 +362,99 @@
   </si>
   <si>
     <t>https://store.fut-electronics.com/products/l297-stepper-motor-controller-ic?_pos=16&amp;_sid=6e81b72a6&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>Mecanum Wheel 65mm</t>
+  </si>
+  <si>
+    <t>Mecanum Wheel 65mm + 6.7mm Coupling</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/ro-wheel-mcnamum-65mm-mecanum-wheel-65mm-6-7mm-coupling-8263</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/ro-wheel-mcnamum-76mm-mecanum-wheel-76mm-6-7mm-coupling-8264</t>
+  </si>
+  <si>
+    <t>Mecanum Wheel 76mm</t>
+  </si>
+  <si>
+    <t>Mecanum Wheel 76mm + 6.7mm Coupling</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/mecanum-wheel-80mm-coupling-9343#attr=163</t>
+  </si>
+  <si>
+    <t>Mecanum wheel 80mm</t>
+  </si>
+  <si>
+    <t>Mecanum wheel 80mm + Coupling</t>
+  </si>
+  <si>
+    <t>Metal Caster Wheel 30 mm</t>
+  </si>
+  <si>
+    <t>Metal Caster Wheel 30 mm - Robot Wheel (Max. load 30Kg)</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/ro-wheel-caster-big-30kg-metal-caster-wheel-30-mm-robot-wheel-max-load-30kg-6773</t>
+  </si>
+  <si>
+    <t>Robot Tires 120x60mm </t>
+  </si>
+  <si>
+    <t>Robot Tires 120x60mm + Metal Coupler - Off Road (1 Wheel) RS003CS</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/ro-wheel-rs003cs-robot-tires-120x60mm-metal-coupler-off-road-1-wheel-rs003cs-6684</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/ro-wheel-rw002-robot-wheels-65x26mm-for-mini-dc-gearbox-yellow-motors-2-tires-rw002-8808</t>
+  </si>
+  <si>
+    <t>Robot Wheels 65x26mm</t>
+  </si>
+  <si>
+    <t>Robot Wheels 65x26mm For Mini DC Gearbox Yellow Motors (2 Tires) RW002</t>
+  </si>
+  <si>
+    <t>Robot Tires 85x38mm</t>
+  </si>
+  <si>
+    <t>Robot Tires 85x38mm + Metal Coupler - Off Road (1 Wheel)</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/ro-wheel-85mm-robot-tires-85x38mm-metal-coupler-off-road-1-wheel-8044</t>
+  </si>
+  <si>
+    <t>STM32F103C8T6</t>
+  </si>
+  <si>
+    <t>STM32F103C8T6 ARM STM32 Minimum System Development Board (Debugging Function) Original Chip</t>
+  </si>
+  <si>
+    <t>https://www.ram-e-shop.com/shop/kit-stm32f103-debug-stm32f103c8t6-arm-stm32-minimum-system-development-board-debugging-function-original-chip-8857</t>
+  </si>
+  <si>
+    <t>STM32F103C8T6 - STM32 Development Board original (The Blue Pill)</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/copy-of-stm32f103c8t6-stm32-development-board-original-ic-the-blue-pill?_pos=1&amp;_sid=6d7ebc2cb&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/stm32f103c6t6-development-board?_pos=2&amp;_sid=6d7ebc2cb&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>STM32F103C6T6</t>
+  </si>
+  <si>
+    <t>STM32F103C6T6 (STM32 Minimum System Development Board)</t>
+  </si>
+  <si>
+    <t>https://store.fut-electronics.com/products/stm32f103c8t6-stm32-development-board-original-the-blue-pill-copy?_pos=3&amp;_sid=6d7ebc2cb&amp;_ss=r</t>
+  </si>
+  <si>
+    <t>STM32F103C8T6 - STM32 Development Board original (The Blue Pill) WEACT</t>
   </si>
 </sst>
 </file>
@@ -748,11 +841,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -833,7 +926,7 @@
         <v>260</v>
       </c>
       <c r="E3" s="6">
-        <f t="shared" ref="E3:E44" si="0">C3*D3</f>
+        <f t="shared" ref="E3:E49" si="0">C3*D3</f>
         <v>260</v>
       </c>
       <c r="F3" s="7" t="s">
@@ -1535,7 +1628,7 @@
       <c r="A28" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="6" t="s">
         <v>95</v>
       </c>
       <c r="C28" s="6">
@@ -1562,7 +1655,7 @@
       <c r="A29" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="6" t="s">
         <v>99</v>
       </c>
       <c r="C29" s="6">
@@ -1616,7 +1709,7 @@
       <c r="A31" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="6" t="s">
         <v>105</v>
       </c>
       <c r="C31" s="6">
@@ -1643,7 +1736,7 @@
       <c r="A32" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="6" t="s">
         <v>107</v>
       </c>
       <c r="C32" s="6">
@@ -1670,7 +1763,7 @@
       <c r="A33" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="6" t="s">
         <v>109</v>
       </c>
       <c r="C33" s="6">
@@ -1697,7 +1790,7 @@
       <c r="A34" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="6" t="s">
         <v>112</v>
       </c>
       <c r="C34" s="6">
@@ -1720,112 +1813,371 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="9"/>
+    <row r="35" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="C35" s="6">
         <v>1</v>
       </c>
+      <c r="D35" s="1">
+        <v>225</v>
+      </c>
       <c r="E35" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>225</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>119</v>
+      </c>
       <c r="C36" s="6">
         <v>1</v>
       </c>
+      <c r="D36" s="1">
+        <v>300</v>
+      </c>
       <c r="E36" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="C37" s="6">
         <v>1</v>
       </c>
+      <c r="D37" s="1">
+        <v>200</v>
+      </c>
       <c r="E37" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A38" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>124</v>
+      </c>
       <c r="C38" s="6">
         <v>1</v>
       </c>
+      <c r="D38" s="1">
+        <v>45</v>
+      </c>
       <c r="E38" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A39" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>127</v>
+      </c>
       <c r="C39" s="6">
         <v>1</v>
       </c>
+      <c r="D39" s="1">
+        <v>400</v>
+      </c>
       <c r="E39" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>128</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="6">
+        <v>1</v>
+      </c>
+      <c r="D40" s="1">
+        <v>50</v>
+      </c>
       <c r="E40" s="6">
         <f>C40*D40</f>
+        <v>50</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A41" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41" s="6">
+        <v>1</v>
+      </c>
+      <c r="D41" s="1">
+        <v>240</v>
+      </c>
+      <c r="E41" s="6">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1</v>
+      </c>
+      <c r="D42" s="1">
+        <v>235</v>
+      </c>
+      <c r="E42" s="6">
+        <f t="shared" si="0"/>
+        <v>235</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C43" s="6">
+        <v>1</v>
+      </c>
+      <c r="D43" s="1">
+        <v>170</v>
+      </c>
+      <c r="E43" s="6">
+        <f t="shared" si="0"/>
+        <v>170</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A44" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C44" s="6">
+        <v>1</v>
+      </c>
+      <c r="D44" s="1">
+        <v>140</v>
+      </c>
+      <c r="E44" s="6">
+        <f t="shared" si="0"/>
+        <v>140</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1</v>
+      </c>
+      <c r="D45" s="1">
+        <v>320</v>
+      </c>
+      <c r="E45" s="6">
+        <f t="shared" si="0"/>
+        <v>320</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="9"/>
+      <c r="C46" s="6">
+        <v>1</v>
+      </c>
+      <c r="E46" s="6">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E41" s="6">
+      <c r="F46" s="7"/>
+      <c r="H46" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="9"/>
+      <c r="C47" s="6">
+        <v>1</v>
+      </c>
+      <c r="E47" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E42" s="6">
+      <c r="H47" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="9"/>
+      <c r="C48" s="6">
+        <v>1</v>
+      </c>
+      <c r="E48" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E43" s="6">
+    <row r="49" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="9"/>
+      <c r="C49" s="6">
+        <v>1</v>
+      </c>
+      <c r="E49" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E44" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+    <row r="50" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="9"/>
+    </row>
+    <row r="51" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="9"/>
+    </row>
+    <row r="52" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="9"/>
+    </row>
+    <row r="53" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36:H56" xr:uid="{D626CD92-1D31-4F2E-84BE-B83415C68F3E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H48:H56" xr:uid="{D626CD92-1D31-4F2E-84BE-B83415C68F3E}">
       <formula1>$L$4:$L$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G39" xr:uid="{9524383D-FF88-4EBF-A2C1-6C00F40D5ACB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G45" xr:uid="{9524383D-FF88-4EBF-A2C1-6C00F40D5ACB}">
       <formula1>$K$4:$K$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H35" xr:uid="{688D04B9-EF58-4BA7-8B5E-526FB7D00083}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H47" xr:uid="{688D04B9-EF58-4BA7-8B5E-526FB7D00083}">
       <formula1>$L$4:$L$9</formula1>
     </dataValidation>
   </dataValidations>
